--- a/artfynd/A 14755-2025 artfynd.xlsx
+++ b/artfynd/A 14755-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113566845</v>
+        <v>113566844</v>
       </c>
       <c r="B2" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458854</v>
+        <v>458871</v>
       </c>
       <c r="R2" t="n">
-        <v>6516009</v>
+        <v>6516038</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -774,6 +769,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113566845</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hallsberg-timmersdala, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>458854</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6516009</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Töreboda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älgarås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
